--- a/database_penyimpanan_aman/database_status_pembayaran.xlsx
+++ b/database_penyimpanan_aman/database_status_pembayaran.xlsx
@@ -413,314 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nomor Kontrak</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nomor Invoice</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Tanggal Invoice</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Tanggal Penyerahan</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TOP Hari</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Tanggal Jatuh Tempo</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Status Pembayaran</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Tanggal Pelunasan</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Catatan</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Update Terakhir</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Nomor Faktur Pajak</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Durasi Riil Hari</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>7207250142</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>037/BSS-JOB/II/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>73803990</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Lunas</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-09-10 20:39:33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>7207250142</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>036/BSS-JOB/II/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>30</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>51177360</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Lunas</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-09-10 20:40:45</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>7201250141</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>127/BSS-JOB/VI/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>890007884.9999999</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Belum Dibayar</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-09-10 22:31:41</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>3002600226134177</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>126/BSS-JOB/VI/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>6919250</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Lunas</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lunas terbayar di pootong pph  </t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-09-11 10:40:22</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>4002600226111627.0</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/database_penyimpanan_aman/database_status_pembayaran.xlsx
+++ b/database_penyimpanan_aman/database_status_pembayaran.xlsx
@@ -413,9 +413,276 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nomor Kontrak</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nomor Invoice</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Nomor Faktur Pajak</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Tanggal Invoice</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Tanggal Penyerahan</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>TOP Hari</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Tanggal Jatuh Tempo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Tanggal Pelunasan</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Durasi Riil Hari</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Nilai DPP</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Nilai PPN</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Nominal Pembayaran Aktual</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Potongan PPh</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Potongan PPN WAPU</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Selisih Lainnya</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Status Pembayaran</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Update Terakhir</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7203250036</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>468/BSS-JOB/XII/2025</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3002500399306811</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>34</v>
+      </c>
+      <c r="K2" t="n">
+        <v>61047000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6715170</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67762170</v>
+      </c>
+      <c r="N2" t="n">
+        <v>59826060</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1220940</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6715170</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Lengkap</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:13:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/II/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>03002600024545726</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>42</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24499020</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2694892.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>27193912.2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>24009040</v>
+      </c>
+      <c r="O3" t="n">
+        <v>489980</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2694892</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.1999999992549419</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Dibayar</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Lengkap</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:55:22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/database_penyimpanan_aman/database_status_pembayaran.xlsx
+++ b/database_penyimpanan_aman/database_status_pembayaran.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,20 +599,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="A3" t="n">
+        <v>7207250142</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>035/BSS-JOB/II/2026</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>03002600024545726</t>
-        </is>
+      <c r="C3" t="n">
+        <v>3002600024545726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -679,6 +675,86 @@
       <c r="T3" t="inlineStr">
         <is>
           <t>2026-09-15 04:55:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>126/BSS-JOB/VI/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>29</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6919250</v>
+      </c>
+      <c r="L4" t="n">
+        <v>761117.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7680367.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7541983</v>
+      </c>
+      <c r="O4" t="n">
+        <v>138385</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Dibayar</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Lengkap</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:20:21</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_status_pembayaran.xlsx
+++ b/database_penyimpanan_aman/database_status_pembayaran.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,10 +679,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A4" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -755,6 +753,90 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>2026-09-15 08:20:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>127/BSS-JOB/VI/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>03002600226134177</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" t="n">
+        <v>890007885</v>
+      </c>
+      <c r="L5" t="n">
+        <v>97900867.34999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>987908752.35</v>
+      </c>
+      <c r="N5" t="n">
+        <v>887686125</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2321759.7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>97900867.34999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.2999999523162842</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Dibayar</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Lengkap</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:54:12</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_status_pembayaran.xlsx
+++ b/database_penyimpanan_aman/database_status_pembayaran.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,20 +757,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A5" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>127/BSS-JOB/VI/2026</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>03002600226134177</t>
-        </is>
+      <c r="C5" t="n">
+        <v>3002600226134177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -837,6 +833,90 @@
       <c r="T5" t="inlineStr">
         <is>
           <t>2026-09-15 08:54:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>028/BSS-JOB/WS/VIII/2026test</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>04002600355739261</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14459400</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1431480.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14444940.6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>12724272</v>
+      </c>
+      <c r="O6" t="n">
+        <v>289188</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1431480.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Dibayar</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Lengkap</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:24:30</t>
         </is>
       </c>
     </row>
